--- a/data/processed/harmonization/Carbon__Total_carbon/10.15485_1960313/10.15485_1960313_soil_Carbon__Total_carbon.xlsx
+++ b/data/processed/harmonization/Carbon__Total_carbon/10.15485_1960313/10.15485_1960313_soil_Carbon__Total_carbon.xlsx
@@ -431,8 +431,8 @@
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="48" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
     <col width="7" customWidth="1" min="5" max="5"/>
     <col width="6" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
@@ -518,12 +518,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>IEEXG001Q</t>
+          <t>transition:IEEXG001Q</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr"/>
@@ -570,12 +570,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>IEEXG001N</t>
+          <t>upland:IEEXG001N</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr"/>
@@ -622,12 +622,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>IEEXG001K</t>
+          <t>wetland:IEEXG001K</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr"/>
@@ -674,12 +674,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>IEEXG003I</t>
+          <t>transition:IEEXG003I</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr"/>
@@ -726,12 +726,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>IEEXG003F</t>
+          <t>upland:IEEXG003F</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr"/>
@@ -778,12 +778,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>IEEXG003C</t>
+          <t>wetland:IEEXG003C</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr"/>
@@ -830,12 +830,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>IEEXG003Y</t>
+          <t>transition:IEEXG003Y</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr"/>
@@ -882,12 +882,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>IEEXG003V</t>
+          <t>upland:IEEXG003V</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>IEEXG003S</t>
+          <t>wetland:IEEXG003S</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr"/>
@@ -986,12 +986,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>IEEXG004E</t>
+          <t>transition:IEEXG004E</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr"/>
@@ -1038,12 +1038,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>IEEXG004B</t>
+          <t>upland:IEEXG004B</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr"/>
@@ -1090,12 +1090,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>IEEXG0048</t>
+          <t>wetland:IEEXG0048</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr"/>
@@ -1142,12 +1142,12 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>IEEXG004U</t>
+          <t>transition:IEEXG004U</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr"/>
@@ -1194,12 +1194,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>IEEXG004R</t>
+          <t>upland:IEEXG004R</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr"/>
@@ -1246,12 +1246,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>IEEXG004O</t>
+          <t>wetland:IEEXG004O</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr"/>
@@ -1298,12 +1298,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>IEEXG0054</t>
+          <t>wetland:IEEXG0054</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr"/>
@@ -1350,12 +1350,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>IEEXG005Q</t>
+          <t>transition:IEEXG005Q</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr"/>
@@ -1402,12 +1402,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>IEEXG005N</t>
+          <t>upland:IEEXG005N</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr"/>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>IEEXG005K</t>
+          <t>wetland:IEEXG005K</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr"/>
@@ -1506,12 +1506,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>IEEXG0060</t>
+          <t>wetland:IEEXG0060</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr"/>
@@ -1558,12 +1558,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>IEEXG006M</t>
+          <t>transition:IEEXG006M</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr"/>
@@ -1610,12 +1610,12 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>IEEXG006J</t>
+          <t>upland:IEEXG006J</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr"/>
@@ -1662,12 +1662,12 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>IEEXG006G</t>
+          <t>wetland:IEEXG006G</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr"/>
@@ -1714,12 +1714,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>IEEXG0072</t>
+          <t>transition:IEEXG0072</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr"/>
@@ -1766,12 +1766,12 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>IEEXG006Z</t>
+          <t>upland:IEEXG006Z</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr"/>
@@ -1818,12 +1818,12 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>IEEXG006W</t>
+          <t>wetland:IEEXG006W</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr"/>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>IEEXG007I</t>
+          <t>transition:IEEXG007I</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr"/>
@@ -1922,12 +1922,12 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>IEEXG007F</t>
+          <t>upland:IEEXG007F</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr"/>
@@ -1974,12 +1974,12 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>IEEXG007C</t>
+          <t>wetland:IEEXG007C</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr"/>
@@ -2026,12 +2026,12 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>IEEXG008E</t>
+          <t>transition:IEEXG008E</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr"/>
@@ -2078,12 +2078,12 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>IEEXG008B</t>
+          <t>upland:IEEXG008B</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr"/>
@@ -2130,12 +2130,12 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>IEEXG008R</t>
+          <t>upland:IEEXG008R</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr"/>
@@ -2182,12 +2182,12 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>IEEXG009A</t>
+          <t>transition:IEEXG009A</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr"/>
@@ -2234,12 +2234,12 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>IEEXG0097</t>
+          <t>upland:IEEXG0097</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr"/>
@@ -2286,12 +2286,12 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>IEEXG0094</t>
+          <t>wetland:IEEXG0094</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr"/>
@@ -2338,12 +2338,12 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>IEEXG009Q</t>
+          <t>transition:IEEXG009Q</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr"/>
@@ -2390,12 +2390,12 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>IEEXG009N</t>
+          <t>upland:IEEXG009N</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr"/>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00A3</t>
+          <t>upland:IEEXG00A3</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr"/>
@@ -2494,12 +2494,12 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00A0</t>
+          <t>wetland:IEEXG00A0</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr"/>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00AM</t>
+          <t>transition:IEEXG00AM</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr"/>
@@ -2598,12 +2598,12 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00AJ</t>
+          <t>upland:IEEXG00AJ</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr"/>
@@ -2650,12 +2650,12 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00B2</t>
+          <t>transition:IEEXG00B2</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr"/>
@@ -2702,12 +2702,12 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00AZ</t>
+          <t>upland:IEEXG00AZ</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr"/>
@@ -2754,12 +2754,12 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00AW</t>
+          <t>wetland:IEEXG00AW</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr"/>
@@ -2806,12 +2806,12 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00BI</t>
+          <t>transition:IEEXG00BI</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr"/>
@@ -2858,12 +2858,12 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00BF</t>
+          <t>upland:IEEXG00BF</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr"/>
@@ -2910,12 +2910,12 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00BC</t>
+          <t>wetland:IEEXG00BC</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr"/>
@@ -2962,12 +2962,12 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00CU</t>
+          <t>transition:IEEXG00CU</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr"/>
@@ -3014,12 +3014,12 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00CR</t>
+          <t>upland:IEEXG00CR</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr"/>
@@ -3066,12 +3066,12 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00CO</t>
+          <t>wetland:IEEXG00CO</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr"/>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00D7</t>
+          <t>upland:IEEXG00D7</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr"/>
@@ -3170,12 +3170,12 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00D4</t>
+          <t>wetland:IEEXG00D4</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr"/>
@@ -3222,12 +3222,12 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00EJ</t>
+          <t>upland:IEEXG00EJ</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr"/>
@@ -3274,12 +3274,12 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00EG</t>
+          <t>wetland:IEEXG00EG</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr"/>
@@ -3326,12 +3326,12 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00F2</t>
+          <t>transition:IEEXG00F2</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr"/>
@@ -3378,12 +3378,12 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00EZ</t>
+          <t>upland:IEEXG00EZ</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr"/>
@@ -3430,12 +3430,12 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00EW</t>
+          <t>wetland:IEEXG00EW</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr"/>
@@ -3482,12 +3482,12 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00FI</t>
+          <t>transition:IEEXG00FI</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr"/>
@@ -3534,12 +3534,12 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00FF</t>
+          <t>upland:IEEXG00FF</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr"/>
@@ -3586,12 +3586,12 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00FC</t>
+          <t>wetland:IEEXG00FC</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr"/>
@@ -3638,12 +3638,12 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00FY</t>
+          <t>transition:IEEXG00FY</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr"/>
@@ -3690,12 +3690,12 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00FV</t>
+          <t>upland:IEEXG00FV</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr"/>
@@ -3742,12 +3742,12 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00FS</t>
+          <t>wetland:IEEXG00FS</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr"/>
@@ -3794,12 +3794,12 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00G8</t>
+          <t>wetland:IEEXG00G8</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr"/>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00GR</t>
+          <t>upland:IEEXG00GR</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr"/>
@@ -3898,12 +3898,12 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00GO</t>
+          <t>wetland:IEEXG00GO</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr"/>
@@ -3950,12 +3950,12 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00HA</t>
+          <t>transition:IEEXG00HA</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr"/>
@@ -4002,12 +4002,12 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00H7</t>
+          <t>upland:IEEXG00H7</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr"/>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00H4</t>
+          <t>wetland:IEEXG00H4</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr"/>
@@ -4106,12 +4106,12 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00HQ</t>
+          <t>transition:IEEXG00HQ</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr"/>
@@ -4158,12 +4158,12 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00HN</t>
+          <t>upland:IEEXG00HN</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr"/>
@@ -4210,12 +4210,12 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00HK</t>
+          <t>wetland:IEEXG00HK</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr"/>
@@ -4262,12 +4262,12 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00I6</t>
+          <t>transition:IEEXG00I6</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr"/>
@@ -4314,12 +4314,12 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00I3</t>
+          <t>upland:IEEXG00I3</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr"/>
@@ -4366,12 +4366,12 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00I0</t>
+          <t>wetland:IEEXG00I0</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr"/>
@@ -4418,12 +4418,12 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00IM</t>
+          <t>transition:IEEXG00IM</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr"/>
@@ -4470,12 +4470,12 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00IJ</t>
+          <t>upland:IEEXG00IJ</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr"/>
@@ -4522,12 +4522,12 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00IG</t>
+          <t>wetland:IEEXG00IG</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr"/>
@@ -4574,12 +4574,12 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00JI</t>
+          <t>transition:IEEXG00JI</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr"/>
@@ -4626,12 +4626,12 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00JF</t>
+          <t>upland:IEEXG00JF</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr"/>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00JC</t>
+          <t>wetland:IEEXG00JC</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr"/>
@@ -4730,12 +4730,12 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00JY</t>
+          <t>transition:IEEXG00JY</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr"/>
@@ -4782,12 +4782,12 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00JV</t>
+          <t>upland:IEEXG00JV</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr"/>
@@ -4834,12 +4834,12 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00JS</t>
+          <t>wetland:IEEXG00JS</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr"/>
@@ -4886,12 +4886,12 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00K8</t>
+          <t>wetland:IEEXG00K8</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr"/>
@@ -4938,12 +4938,12 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00KB</t>
+          <t>upland:IEEXG00KB</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr"/>
@@ -4990,12 +4990,12 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00KU</t>
+          <t>transition:IEEXG00KU</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr"/>
@@ -5042,12 +5042,12 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00KR</t>
+          <t>upland:IEEXG00KR</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr"/>
@@ -5094,12 +5094,12 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00KO</t>
+          <t>wetland:IEEXG00KO</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr"/>
@@ -5146,12 +5146,12 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00LA</t>
+          <t>transition:IEEXG00LA</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr"/>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00L7</t>
+          <t>upland:IEEXG00L7</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr"/>
@@ -5250,12 +5250,12 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00L4</t>
+          <t>wetland:IEEXG00L4</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr"/>
@@ -5302,12 +5302,12 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00LQ</t>
+          <t>transition:IEEXG00LQ</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr"/>
@@ -5354,12 +5354,12 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00LN</t>
+          <t>upland:IEEXG00LN</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr"/>
@@ -5406,12 +5406,12 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00M6</t>
+          <t>transition:IEEXG00M6</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr"/>
@@ -5458,12 +5458,12 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00M3</t>
+          <t>upland:IEEXG00M3</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr"/>
@@ -5510,12 +5510,12 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00M0</t>
+          <t>wetland:IEEXG00M0</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr"/>
@@ -5562,12 +5562,12 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00MM</t>
+          <t>transition:IEEXG00MM</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr"/>
@@ -5614,12 +5614,12 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00MJ</t>
+          <t>upland:IEEXG00MJ</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr"/>
@@ -5666,12 +5666,12 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00MG</t>
+          <t>wetland:IEEXG00MG</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr"/>
@@ -5718,12 +5718,12 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00N2</t>
+          <t>transition:IEEXG00N2</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr"/>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00MZ</t>
+          <t>upland:IEEXG00MZ</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr"/>
@@ -5822,12 +5822,12 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00NI</t>
+          <t>transition:IEEXG00NI</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr"/>
@@ -5874,12 +5874,12 @@
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00NF</t>
+          <t>upland:IEEXG00NF</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr"/>
@@ -5926,12 +5926,12 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00NC</t>
+          <t>wetland:IEEXG00NC</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr"/>
@@ -5978,12 +5978,12 @@
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00NY</t>
+          <t>transition:IEEXG00NY</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr"/>
@@ -6030,12 +6030,12 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00NV</t>
+          <t>upland:IEEXG00NV</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr"/>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00NS</t>
+          <t>wetland:IEEXG00NS</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr"/>
@@ -6134,12 +6134,12 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00OB</t>
+          <t>upland:IEEXG00OB</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr"/>
@@ -6186,12 +6186,12 @@
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00OU</t>
+          <t>transition:IEEXG00OU</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr"/>
@@ -6238,12 +6238,12 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00OR</t>
+          <t>upland:IEEXG00OR</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr"/>
@@ -6290,12 +6290,12 @@
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00OO</t>
+          <t>wetland:IEEXG00OO</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr"/>
@@ -6342,12 +6342,12 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00PQ</t>
+          <t>transition:IEEXG00PQ</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr"/>
@@ -6394,12 +6394,12 @@
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00PN</t>
+          <t>upland:IEEXG00PN</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr"/>
@@ -6446,12 +6446,12 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00PK</t>
+          <t>wetland:IEEXG00PK</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr"/>
@@ -6498,12 +6498,12 @@
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00Q6</t>
+          <t>transition:IEEXG00Q6</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr"/>
@@ -6550,12 +6550,12 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00Q3</t>
+          <t>upland:IEEXG00Q3</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr"/>
@@ -6602,12 +6602,12 @@
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00Q0</t>
+          <t>wetland:IEEXG00Q0</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr"/>
@@ -6654,12 +6654,12 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00R2</t>
+          <t>transition:IEEXG00R2</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr"/>
@@ -6706,12 +6706,12 @@
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00QZ</t>
+          <t>upland:IEEXG00QZ</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr"/>
@@ -6758,12 +6758,12 @@
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00QW</t>
+          <t>wetland:IEEXG00QW</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr"/>
@@ -6810,12 +6810,12 @@
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00RI</t>
+          <t>transition:IEEXG00RI</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr"/>
@@ -6862,12 +6862,12 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00RF</t>
+          <t>upland:IEEXG00RF</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr"/>
@@ -6914,12 +6914,12 @@
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00RC</t>
+          <t>wetland:IEEXG00RC</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr"/>

--- a/data/processed/harmonization/Carbon__Total_carbon/10.15485_1960313/10.15485_1960313_soil_Carbon__Total_carbon.xlsx
+++ b/data/processed/harmonization/Carbon__Total_carbon/10.15485_1960313/10.15485_1960313_soil_Carbon__Total_carbon.xlsx
@@ -537,7 +537,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -553,7 +553,7 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -589,7 +589,7 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I3" t="n">
@@ -605,7 +605,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I4" t="n">
@@ -657,7 +657,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -693,7 +693,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I5" t="n">
@@ -709,7 +709,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I6" t="n">
@@ -761,7 +761,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I7" t="n">
@@ -813,7 +813,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I8" t="n">
@@ -865,7 +865,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -901,7 +901,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I9" t="n">
@@ -917,7 +917,7 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -953,7 +953,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I10" t="n">
@@ -969,7 +969,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -1005,7 +1005,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I11" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -1057,7 +1057,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I12" t="n">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I13" t="n">
@@ -1125,7 +1125,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I14" t="n">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I15" t="n">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -1265,7 +1265,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I16" t="n">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -1317,7 +1317,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I17" t="n">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I18" t="n">
@@ -1385,7 +1385,7 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I19" t="n">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I20" t="n">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -1525,7 +1525,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I21" t="n">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -1577,7 +1577,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I22" t="n">
@@ -1593,7 +1593,7 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I23" t="n">
@@ -1645,7 +1645,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -1681,7 +1681,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I24" t="n">
@@ -1697,7 +1697,7 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -1733,7 +1733,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I25" t="n">
@@ -1749,7 +1749,7 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -1785,7 +1785,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I26" t="n">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -1837,7 +1837,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I27" t="n">
@@ -1853,7 +1853,7 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I28" t="n">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -1941,7 +1941,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I29" t="n">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -1993,7 +1993,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I30" t="n">
@@ -2009,7 +2009,7 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -2045,7 +2045,7 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I31" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I32" t="n">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I33" t="n">
@@ -2165,7 +2165,7 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -2201,7 +2201,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I34" t="n">
@@ -2217,7 +2217,7 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I35" t="n">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -2305,7 +2305,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I36" t="n">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -2357,7 +2357,7 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I37" t="n">
@@ -2373,7 +2373,7 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I38" t="n">
@@ -2425,7 +2425,7 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -2461,7 +2461,7 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I39" t="n">
@@ -2477,7 +2477,7 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -2513,7 +2513,7 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I40" t="n">
@@ -2529,7 +2529,7 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I41" t="n">
@@ -2581,7 +2581,7 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -2617,7 +2617,7 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I42" t="n">
@@ -2633,7 +2633,7 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -2669,7 +2669,7 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I43" t="n">
@@ -2685,7 +2685,7 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -2721,7 +2721,7 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I44" t="n">
@@ -2737,7 +2737,7 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -2773,7 +2773,7 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I45" t="n">
@@ -2789,7 +2789,7 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -2825,7 +2825,7 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I46" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -2877,7 +2877,7 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I47" t="n">
@@ -2893,7 +2893,7 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I48" t="n">
@@ -2945,7 +2945,7 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -2981,7 +2981,7 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I49" t="n">
@@ -2997,7 +2997,7 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I50" t="n">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -3085,7 +3085,7 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I51" t="n">
@@ -3101,7 +3101,7 @@
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -3137,7 +3137,7 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I52" t="n">
@@ -3153,7 +3153,7 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -3189,7 +3189,7 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I53" t="n">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I54" t="n">
@@ -3257,7 +3257,7 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -3293,7 +3293,7 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I55" t="n">
@@ -3309,7 +3309,7 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I56" t="n">
@@ -3361,7 +3361,7 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -3397,7 +3397,7 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I57" t="n">
@@ -3413,7 +3413,7 @@
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -3449,7 +3449,7 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I58" t="n">
@@ -3465,7 +3465,7 @@
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -3501,7 +3501,7 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I59" t="n">
@@ -3517,7 +3517,7 @@
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -3553,7 +3553,7 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I60" t="n">
@@ -3569,7 +3569,7 @@
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -3605,7 +3605,7 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I61" t="n">
@@ -3621,7 +3621,7 @@
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -3657,7 +3657,7 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I62" t="n">
@@ -3673,7 +3673,7 @@
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -3709,7 +3709,7 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I63" t="n">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -3761,7 +3761,7 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I64" t="n">
@@ -3777,7 +3777,7 @@
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -3813,7 +3813,7 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I65" t="n">
@@ -3829,7 +3829,7 @@
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -3865,7 +3865,7 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I66" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -3917,7 +3917,7 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I67" t="n">
@@ -3933,7 +3933,7 @@
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -3969,7 +3969,7 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I68" t="n">
@@ -3985,7 +3985,7 @@
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -4021,7 +4021,7 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I69" t="n">
@@ -4037,7 +4037,7 @@
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -4073,7 +4073,7 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I70" t="n">
@@ -4089,7 +4089,7 @@
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I71" t="n">
@@ -4141,7 +4141,7 @@
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -4177,7 +4177,7 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I72" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -4229,7 +4229,7 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I73" t="n">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -4281,7 +4281,7 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I74" t="n">
@@ -4297,7 +4297,7 @@
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -4333,7 +4333,7 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I75" t="n">
@@ -4349,7 +4349,7 @@
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -4385,7 +4385,7 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I76" t="n">
@@ -4401,7 +4401,7 @@
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -4437,7 +4437,7 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I77" t="n">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -4489,7 +4489,7 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I78" t="n">
@@ -4505,7 +4505,7 @@
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -4541,7 +4541,7 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I79" t="n">
@@ -4557,7 +4557,7 @@
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -4593,7 +4593,7 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I80" t="n">
@@ -4609,7 +4609,7 @@
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -4645,7 +4645,7 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I81" t="n">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -4697,7 +4697,7 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I82" t="n">
@@ -4713,7 +4713,7 @@
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -4749,7 +4749,7 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I83" t="n">
@@ -4765,7 +4765,7 @@
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -4801,7 +4801,7 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I84" t="n">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I85" t="n">
@@ -4869,7 +4869,7 @@
       </c>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -4905,7 +4905,7 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I86" t="n">
@@ -4921,7 +4921,7 @@
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -4957,7 +4957,7 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I87" t="n">
@@ -4973,7 +4973,7 @@
       </c>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -5009,7 +5009,7 @@
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I88" t="n">
@@ -5025,7 +5025,7 @@
       </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -5061,7 +5061,7 @@
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I89" t="n">
@@ -5077,7 +5077,7 @@
       </c>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -5113,7 +5113,7 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I90" t="n">
@@ -5129,7 +5129,7 @@
       </c>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -5165,7 +5165,7 @@
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I91" t="n">
@@ -5181,7 +5181,7 @@
       </c>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -5217,7 +5217,7 @@
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I92" t="n">
@@ -5233,7 +5233,7 @@
       </c>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -5269,7 +5269,7 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I93" t="n">
@@ -5285,7 +5285,7 @@
       </c>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -5321,7 +5321,7 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I94" t="n">
@@ -5337,7 +5337,7 @@
       </c>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -5373,7 +5373,7 @@
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I95" t="n">
@@ -5389,7 +5389,7 @@
       </c>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -5425,7 +5425,7 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I96" t="n">
@@ -5441,7 +5441,7 @@
       </c>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -5477,7 +5477,7 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I97" t="n">
@@ -5493,7 +5493,7 @@
       </c>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -5529,7 +5529,7 @@
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I98" t="n">
@@ -5545,7 +5545,7 @@
       </c>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I99" t="n">
@@ -5597,7 +5597,7 @@
       </c>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -5633,7 +5633,7 @@
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I100" t="n">
@@ -5649,7 +5649,7 @@
       </c>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -5685,7 +5685,7 @@
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I101" t="n">
@@ -5701,7 +5701,7 @@
       </c>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -5737,7 +5737,7 @@
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I102" t="n">
@@ -5753,7 +5753,7 @@
       </c>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -5789,7 +5789,7 @@
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I103" t="n">
@@ -5805,7 +5805,7 @@
       </c>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -5841,7 +5841,7 @@
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I104" t="n">
@@ -5857,7 +5857,7 @@
       </c>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I105" t="n">
@@ -5909,7 +5909,7 @@
       </c>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -5945,7 +5945,7 @@
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I106" t="n">
@@ -5961,7 +5961,7 @@
       </c>
       <c r="L106" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -5997,7 +5997,7 @@
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I107" t="n">
@@ -6013,7 +6013,7 @@
       </c>
       <c r="L107" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -6049,7 +6049,7 @@
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I108" t="n">
@@ -6065,7 +6065,7 @@
       </c>
       <c r="L108" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -6101,7 +6101,7 @@
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I109" t="n">
@@ -6117,7 +6117,7 @@
       </c>
       <c r="L109" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -6153,7 +6153,7 @@
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I110" t="n">
@@ -6169,7 +6169,7 @@
       </c>
       <c r="L110" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -6205,7 +6205,7 @@
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I111" t="n">
@@ -6221,7 +6221,7 @@
       </c>
       <c r="L111" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -6257,7 +6257,7 @@
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I112" t="n">
@@ -6273,7 +6273,7 @@
       </c>
       <c r="L112" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I113" t="n">
@@ -6325,7 +6325,7 @@
       </c>
       <c r="L113" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -6361,7 +6361,7 @@
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I114" t="n">
@@ -6377,7 +6377,7 @@
       </c>
       <c r="L114" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -6413,7 +6413,7 @@
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I115" t="n">
@@ -6429,7 +6429,7 @@
       </c>
       <c r="L115" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -6465,7 +6465,7 @@
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I116" t="n">
@@ -6481,7 +6481,7 @@
       </c>
       <c r="L116" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -6517,7 +6517,7 @@
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I117" t="n">
@@ -6533,7 +6533,7 @@
       </c>
       <c r="L117" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -6569,7 +6569,7 @@
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I118" t="n">
@@ -6585,7 +6585,7 @@
       </c>
       <c r="L118" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -6621,7 +6621,7 @@
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I119" t="n">
@@ -6637,7 +6637,7 @@
       </c>
       <c r="L119" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -6673,7 +6673,7 @@
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I120" t="n">
@@ -6689,7 +6689,7 @@
       </c>
       <c r="L120" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I121" t="n">
@@ -6741,7 +6741,7 @@
       </c>
       <c r="L121" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -6777,7 +6777,7 @@
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I122" t="n">
@@ -6793,7 +6793,7 @@
       </c>
       <c r="L122" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -6829,7 +6829,7 @@
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I123" t="n">
@@ -6845,7 +6845,7 @@
       </c>
       <c r="L123" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -6881,7 +6881,7 @@
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I124" t="n">
@@ -6897,7 +6897,7 @@
       </c>
       <c r="L124" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
@@ -6933,7 +6933,7 @@
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I125" t="n">
@@ -6949,7 +6949,7 @@
       </c>
       <c r="L125" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1960313 package spatialCoverage named point; data key kit_id; source column carbon_weight_perc (percent, unit from data dictionary); date 2021 from package temporal coverage; method from cited paper doi:10.1038/s41597-023-02548-7</t>
         </is>
       </c>
     </row>
